--- a/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けですね。続きは、またの機会に。</t>
+          <t xml:space="preserve">決着つかずですね。続きは、またの機会に。</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けというのは、いちばん困りますね。</t>
+          <t xml:space="preserve">決着がつかないというのは、いちばん困りますね。</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.polite[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.polite[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3529,14 +3529,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残らせていただきます。ここが、わたくしの居場所ですから</t>
+          <t xml:space="preserve">ベルトには手が届きませんでした。ですが、悔いはございません</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.polite[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.polite[2]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。前向きに検討させていただきます</t>
+          <t xml:space="preserve">夢は叶いませんでしたが…この道を選んだことは、よかったと思います</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.polite[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3578,61 +3578,61 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.polite[1]</t>
+          <t xml:space="preserve">A3_heel.normal.polite[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残りたい気持ちはあります。…条件を聞かせてください</t>
+          <t xml:space="preserve">…お泣きにならないでください。みっともないですよ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.polite[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">A3_heel.normal.polite[2]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼ながら、意見を申し上げさせてください。</t>
+          <t xml:space="preserve">わたしがいなくなれば、寂しくなりますよ</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.polite[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3642,29 +3642,29 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.polite[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが変わった気がします。…成長できている実感があります</t>
+          <t xml:space="preserve">ここが、わたしの全部でした</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.polite[2]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3674,29 +3674,29 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.polite[2]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが掴めそうな気がします。もう少しで…</t>
+          <t xml:space="preserve">この団体で過ごした時間は、無駄ではありませんでした</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.polite[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3706,29 +3706,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.polite[1]</t>
+          <t xml:space="preserve">B1_young.normal.polite[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られただけで、幸せです</t>
+          <t xml:space="preserve">まだ何ひとつ、成し遂げられていないのに…</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.polite[2]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3738,29 +3738,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.polite[1]</t>
+          <t xml:space="preserve">B1_young.normal.polite[2]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、皆さんのおかげです</t>
+          <t xml:space="preserve">わたしの物語は…こんなところで終わりなのでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.polite[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3770,29 +3770,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.polite[1]</t>
+          <t xml:space="preserve">B2_prime.normal.polite[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しずつですが、成長を実感しています</t>
+          <t xml:space="preserve">体が…もう言うことを聞いてくれないんです</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.polite[2]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3802,29 +3802,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.polite[1]</t>
+          <t xml:space="preserve">B2_prime.normal.polite[2]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この場所に立たせていただけるなんて…身に余る光栄です</t>
+          <t xml:space="preserve">これからだったのに…悔しいです、本当に…</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.polite[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3834,29 +3834,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.polite[1]</t>
+          <t xml:space="preserve">B3_older.normal.polite[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださる方が増えて、嬉しいです</t>
+          <t xml:space="preserve">わかっていました。いつか来ると</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.polite[2]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3866,29 +3866,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.polite[1]</t>
+          <t xml:space="preserve">B3_older.normal.polite[2]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに多くの方に応援いただいて…感謝の気持ちでいっぱいです</t>
+          <t xml:space="preserve">十分やれました。自分を褒めてやりたいです</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.polite[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3898,29 +3898,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.polite[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…何のために戦っているのか、わからなくなってきました</t>
+          <t xml:space="preserve">このベルト…まだお返ししたくありませんでした</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.polite[2]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3930,29 +3930,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.polite[2]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…戦う理由を思い出しました</t>
+          <t xml:space="preserve">最後の防衛戦、やりたかったです…</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
@@ -3972,19 +3972,19 @@
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…調子が戻ってきた気がします</t>
+          <t xml:space="preserve">残らせていただきます。ここが、わたくしの居場所ですから</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.polite[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3994,29 +3994,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.polite[1]</t>
+          <t xml:space="preserve">raise_accept.normal.polite[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、何をやってもうまくいかなくて…</t>
+          <t xml:space="preserve">ありがとうございます。今後とも、どうぞよろしくお願いいたします。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.polite[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -4026,29 +4026,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.normal.polite[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でした。…相手に感謝しています</t>
+          <t xml:space="preserve">上げていただけるのなら、ありがたいです。頑張りますね。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.polite[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4058,29 +4058,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.normal.polite[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間、ベルトを守り続けることができました。支えてくださった皆さんに感謝します</t>
+          <t xml:space="preserve">……そうですか。かしこまりました。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.polite[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4090,29 +4090,29 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.polite[1]</t>
+          <t xml:space="preserve">raise_open.normal.polite[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入り…夢のようです。支えてくださった全ての方に感謝いたします</t>
+          <t xml:space="preserve">ありがとうございます。前向きに検討させていただきます</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.polite[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4122,29 +4122,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.normal.polite[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余る光栄です。ありがとうございます</t>
+          <t xml:space="preserve">……そうですか。承知いたしました。……少し残念ですけれど。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.polite[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4154,29 +4154,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.normal.polite[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPをいただけるとは…ありがとうございます。来年も頑張ります</t>
+          <t xml:space="preserve">社長、手短に申し上げます。退団させていただきます。もう決めました。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.polite[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4186,29 +4186,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.normal.polite[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで試合ができるなんて、本当に感謝しています</t>
+          <t xml:space="preserve">お世話になりました。ですが、もうここでは続けられません。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.polite[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4218,29 +4218,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">transfer_listen.normal.polite[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日を迎えられて、光栄です</t>
+          <t xml:space="preserve">聞いてくださるんですね。{record}正直、新しい場所で挑戦してみたいんです。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.polite[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4250,29 +4250,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">transfer_open.normal.polite[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くさせていただきます</t>
+          <t xml:space="preserve">社長、お話があります。{tenure}この団体を離れようと考えております。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.polite[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4282,29 +4282,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">transfer_open.normal.polite[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に感謝しかありません</t>
+          <t xml:space="preserve">社長。{tenure}色々と考えたのですが……別の環境でやってみたいのです。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.polite[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4314,29 +4314,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">transfer_release.normal.polite[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます</t>
+          <t xml:space="preserve">……承知しました。{tenure_farewell}{rivalry}お世話になりました。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.polite[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4346,29 +4346,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">transfer_retain_fail.normal.polite[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩は、これからの試合で返します</t>
+          <t xml:space="preserve">……ありがたいのですが……もう、決めたことなんです。申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.polite[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4378,29 +4378,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.normal.polite[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご丁寧な治療を…ありがとうございます。一日でも早く戻ります</t>
+          <t xml:space="preserve">……そこまでしてくださるんですね。……分かりました。もう少し頑張ってみます。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.normal.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.polite[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4410,39 +4410,39 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.normal.polite[1]</t>
+          <t xml:space="preserve">start.normal.polite[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました……!夢みたいです、本当にありがとうございます</t>
+          <t xml:space="preserve">残りたい気持ちはあります。…条件を聞かせてください</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
@@ -4452,19 +4452,19 @@
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日はよろしくお願いいたします</t>
+          <t xml:space="preserve">失礼ながら、意見を申し上げさせてください。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4474,29 +4474,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
+          <t xml:space="preserve">何かが変わった気がします。…成長できている実感があります</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
@@ -4516,19 +4516,19 @@
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
+          <t xml:space="preserve">何かが掴めそうな気がします。もう少しで…</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal.polite[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4538,29 +4538,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">fresh.normal.polite[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
+          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal.polite[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.polite[1]</t>
+          <t xml:space="preserve">heavy.normal.polite[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日はよろしくお願いいたします</t>
+          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.polite[2]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal.polite[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4602,29 +4602,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.polite[2]</t>
+          <t xml:space="preserve">warm.normal.polite[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
+          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.polite[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4634,29 +4634,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.polite[1]</t>
+          <t xml:space="preserve">cap_reached.normal.polite[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
+          <t xml:space="preserve">ここまで来られただけで、幸せです</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.polite[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.polite[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4666,29 +4666,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.polite[2]</t>
+          <t xml:space="preserve">ovr_elite.normal.polite[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
+          <t xml:space="preserve">ここまで来られたのは、皆さんのおかげです</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.polite[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4698,29 +4698,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.polite[1]</t>
+          <t xml:space="preserve">ovr_growth.normal.polite[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
+          <t xml:space="preserve">少しずつですが、成長を実感しています</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.polite[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.polite[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4730,29 +4730,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.polite[2]</t>
+          <t xml:space="preserve">ovr_legend.normal.polite[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
+          <t xml:space="preserve">この場所に立たせていただけるなんて…身に余る光栄です</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.polite[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4762,29 +4762,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">pop_growth.normal.polite[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
+          <t xml:space="preserve">応援してくださる方が増えて、嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.polite[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4794,29 +4794,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">pop_star.normal.polite[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
+          <t xml:space="preserve">こんなに多くの方に応援いただいて…感謝の気持ちでいっぱいです</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4826,29 +4826,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう以前のようには…すみません</t>
+          <t xml:space="preserve">最近…何のために戦っているのか、わからなくなってきました</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4858,29 +4858,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し壁ができたようで…気のせいだといいんですが</t>
+          <t xml:space="preserve">ようやく…戦う理由を思い出しました</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4890,29 +4890,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると自然体でいられます。ありがたいです</t>
+          <t xml:space="preserve">ようやく…調子が戻ってきた気がします</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.polite[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4922,29 +4922,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.polite[1]</t>
+          <t xml:space="preserve">defeat.normal.polite[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なくてはならない方です。心からそう思います</t>
+          <t xml:space="preserve">最近、何をやってもうまくいかなくて…</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.polite[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4954,29 +4954,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.polite[1]</t>
+          <t xml:space="preserve">bestMatch.normal.polite[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も、穏やかになってきました</t>
+          <t xml:space="preserve">最高の試合でした。…相手に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.normal.polite[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4986,29 +4986,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.polite[1]</t>
+          <t xml:space="preserve">champion.normal.polite[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても負けたくないんです…この気持ちは…</t>
+          <t xml:space="preserve">一年間、ベルトを守り続けることができました。支えてくださった皆さんに感謝します</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.polite[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -5018,29 +5018,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.polite[1]</t>
+          <t xml:space="preserve">hallOfFame.normal.polite[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けるわけにはいきません</t>
+          <t xml:space="preserve">殿堂入り…夢のようです。支えてくださった全ての方に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.polite[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5050,29 +5050,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.polite[1]</t>
+          <t xml:space="preserve">mediaAward.normal.polite[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いが…私のプロレス人生そのものです</t>
+          <t xml:space="preserve">身に余る光栄です。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.normal.polite[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5082,29 +5082,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.polite[1]</t>
+          <t xml:space="preserve">mvp.normal.polite[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の一員でいられて…本当に幸せです</t>
+          <t xml:space="preserve">MVPをいただけるとは…ありがとうございます。来年も頑張ります</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5114,29 +5114,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すみません。もう限界かもしれません</t>
+          <t xml:space="preserve">ドームで試合ができるなんて、本当に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[2]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5146,29 +5146,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[2]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…少し不安になってきました…</t>
+          <t xml:space="preserve">今日という日を迎えられて、光栄です</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[3]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5178,29 +5178,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[3]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたが…良い試合ができたと思います</t>
+          <t xml:space="preserve">全力を尽くさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5210,29 +5210,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
+          <t xml:space="preserve">満員のお客様に感謝しかありません</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5242,29 +5242,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[2]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
+          <t xml:space="preserve">社長、本当にありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[3]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5274,29 +5274,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[3]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。応援のおかげです</t>
+          <t xml:space="preserve">この恩は、これからの試合で返します</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.polite[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5306,29 +5306,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.polite[1]</t>
+          <t xml:space="preserve">special_treatment.normal.polite[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
+          <t xml:space="preserve">ご丁寧な治療を…ありがとうございます。一日でも早く戻ります</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.polite[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5338,29 +5338,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.polite[1]</t>
+          <t xml:space="preserve">E1.normal.polite[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し寂しいというか…不安が…</t>
+          <t xml:space="preserve">メディア出演のお話をいただきまして…ご検討いただけますでしょうか</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.polite[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5370,29 +5370,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.polite[1]</t>
+          <t xml:space="preserve">E1.normal.polite[2]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
+          <t xml:space="preserve">出演のお話をいただきました。ぜひ、やらせていただきたいです</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.normal.polite[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5402,29 +5402,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.polite[1]</t>
+          <t xml:space="preserve">E1.accept.normal.polite[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると安心します</t>
+          <t xml:space="preserve">やりました……!夢みたいです、本当にありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5434,29 +5434,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">活躍が気になってしまいます</t>
+          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.polite[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5466,29 +5466,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[2]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
+          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5498,29 +5498,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
+          <t xml:space="preserve">本日はよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.polite[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5530,29 +5530,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[2]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5562,29 +5562,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
+          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.polite[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5594,29 +5594,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[2]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
+          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5626,29 +5626,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
+          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.polite[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5658,29 +5658,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
+          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.polite[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.polite[1]</t>
+          <t xml:space="preserve">normal.polite[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
+          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.polite[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5722,29 +5722,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.polite[2]</t>
+          <t xml:space="preserve">normal.polite[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.polite[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5754,29 +5754,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.polite[3]</t>
+          <t xml:space="preserve">draftInterest.normal.polite[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
+          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.polite[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5786,29 +5786,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.polite[1]</t>
+          <t xml:space="preserve">draftInterest.normal.polite[2]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
+          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.polite[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5818,29 +5818,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.polite[2]</t>
+          <t xml:space="preserve">draftJoin.normal.polite[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
+          <t xml:space="preserve">本日はよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.polite[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5850,29 +5850,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.polite[3]</t>
+          <t xml:space="preserve">draftJoin.normal.polite[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.polite[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5882,29 +5882,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.polite[1]</t>
+          <t xml:space="preserve">faGreeting.normal.polite[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">拾っていただいた御恩は、試合でお返しします</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.polite[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5914,29 +5914,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.polite[2]</t>
+          <t xml:space="preserve">faSigning.normal.polite[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
+          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.polite[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5946,29 +5946,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.polite[3]</t>
+          <t xml:space="preserve">faSigning.normal.polite[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
+          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.polite[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5978,29 +5978,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.polite[1]</t>
+          <t xml:space="preserve">faWelcome.normal.polite[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
+          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.polite[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -6010,29 +6010,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.polite[2]</t>
+          <t xml:space="preserve">faWelcome.normal.polite[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
+          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal.polite[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6042,29 +6042,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.polite[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.normal.polite[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
+          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal.polite[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6074,29 +6074,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.polite[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.normal.polite[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
+          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal.polite[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6106,29 +6106,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.polite[1]</t>
+          <t xml:space="preserve">heatSelf.warm.normal.polite[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
+          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.polite[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6138,29 +6138,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.polite[2]</t>
+          <t xml:space="preserve">injury.normal.polite[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
+          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.polite[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6170,29 +6170,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">injury.normal.polite[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
+          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.polite[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">release.normal.polite[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
+          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.polite[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6234,59 +6234,2299 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">release.normal.polite[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう以前のようには…すみません</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">少し壁ができたようで…気のせいだといいんですが</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒にいると自然体でいられます。ありがたいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なくてはならない方です。心からそう思います</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">関係も、穏やかになってきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どうしても負けたくないんです…この気持ちは…</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">絶対に負けるわけにはいきません</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この戦いが…私のプロレス人生そのものです</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体の一員でいられて…本当に幸せです</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…すみません。もう限界かもしれません</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">すみません…少し不安になってきました…</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.goodLoss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けてしまいましたが…良い試合ができたと思います</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.greatWin.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.loss.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.win.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てました。応援のおかげです</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-02.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-03.down.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">少し寂しいというか…不安が…</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-03.up.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-04.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒にいると安心します</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-05.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">活躍が気になってしまいます</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-06.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-07.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-08.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-09.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-10.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-11.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[3]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.polite[3]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[3]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.polite[3]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[3]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.normal.polite[3]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.normal.polite[2]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.normal.polite[1]</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr" s="2">
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr" s="12">
+      <c r="D250" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.normal.polite[1]</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr" s="2">
+      <c r="E250" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr" s="3">
+      <c r="F250" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最後まで走り切れました。…ありがとうございました</t>
         </is>
       </c>
     </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾っていただいた御恩は、試合でお返しします</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.polite[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H182"/>
+  <autoFilter ref="A1:H252"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
@@ -496,7 +496,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -511,7 +511,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.polite[1]</t>
+          <t xml:space="preserve">atk.polite.normal[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -528,7 +528,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -543,7 +543,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.polite[2]</t>
+          <t xml:space="preserve">atk.polite.normal[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -560,7 +560,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -575,7 +575,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.polite[3]</t>
+          <t xml:space="preserve">atk.polite.normal[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -592,7 +592,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.polite[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -607,7 +607,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.polite[4]</t>
+          <t xml:space="preserve">atk.polite.normal[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -624,7 +624,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.normal[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -639,7 +639,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.polite[1]</t>
+          <t xml:space="preserve">bigmove.polite.normal[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -656,7 +656,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.normal[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -671,7 +671,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.polite[2]</t>
+          <t xml:space="preserve">bigmove.polite.normal[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -688,7 +688,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.normal[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -703,7 +703,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.polite[3]</t>
+          <t xml:space="preserve">bigmove.polite.normal[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -720,7 +720,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.normal[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -735,7 +735,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.polite[1]</t>
+          <t xml:space="preserve">climax.polite.normal[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -752,7 +752,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.normal[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -767,7 +767,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.polite[2]</t>
+          <t xml:space="preserve">climax.polite.normal[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -784,7 +784,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -799,7 +799,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -816,7 +816,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -831,7 +831,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -848,7 +848,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -863,7 +863,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -880,7 +880,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.polite.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -895,7 +895,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal.polite[1]</t>
+          <t xml:space="preserve">badWinner.polite.normal[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -912,7 +912,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.polite.normal[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -927,7 +927,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.polite[1]</t>
+          <t xml:space="preserve">goodWinner.polite.normal[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -944,7 +944,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -959,7 +959,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -976,7 +976,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -1008,7 +1008,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.polite[1]</t>
+          <t xml:space="preserve">loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1040,7 +1040,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.polite[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.polite.normal[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.polite[2]</t>
+          <t xml:space="preserve">loser.polite.normal[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -1072,7 +1072,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.polite[1]</t>
+          <t xml:space="preserve">winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -1104,7 +1104,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.polite[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.polite.normal[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.polite[2]</t>
+          <t xml:space="preserve">winner.polite.normal[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1136,7 +1136,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.polite.normal[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.polite[1]</t>
+          <t xml:space="preserve">competition_won.polite.normal[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1168,7 +1168,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.polite.normal[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.polite[1]</t>
+          <t xml:space="preserve">direct.polite.normal[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1200,7 +1200,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.polite.normal[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.polite[1]</t>
+          <t xml:space="preserve">fa_signing.polite.normal[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1232,7 +1232,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.polite.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.normal.hit[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite.hit[1]</t>
+          <t xml:space="preserve">polite.normal.hit[1]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1264,7 +1264,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.polite.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.normal.hit[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite.hit[2]</t>
+          <t xml:space="preserve">polite.normal.hit[2]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1296,7 +1296,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.polite.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.normal.win[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite.win[1]</t>
+          <t xml:space="preserve">polite.normal.win[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1328,7 +1328,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.polite.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.normal.win[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite.win[2]</t>
+          <t xml:space="preserve">polite.normal.win[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1360,7 +1360,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1392,7 +1392,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1424,7 +1424,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1456,7 +1456,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1488,7 +1488,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1520,7 +1520,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1552,7 +1552,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1584,7 +1584,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1616,7 +1616,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1648,7 +1648,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1680,7 +1680,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1712,7 +1712,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1744,7 +1744,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1776,7 +1776,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1808,7 +1808,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1840,7 +1840,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1872,7 +1872,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.polite[1]</t>
+          <t xml:space="preserve">loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1904,7 +1904,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.polite[1]</t>
+          <t xml:space="preserve">winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1936,7 +1936,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.polite[1]</t>
+          <t xml:space="preserve">loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1968,7 +1968,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.polite[1]</t>
+          <t xml:space="preserve">winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -2000,7 +2000,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -2032,7 +2032,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.polite.normal[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.polite[1]</t>
+          <t xml:space="preserve">defender.polite.normal[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -2064,7 +2064,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -2096,7 +2096,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.polite.normal[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.polite[1]</t>
+          <t xml:space="preserve">defender.polite.normal[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2128,7 +2128,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2160,7 +2160,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.polite.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.polite[1]</t>
+          <t xml:space="preserve">defender.polite.normal[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2192,7 +2192,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.polite[1]</t>
+          <t xml:space="preserve">fateAttacker.polite.normal[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2224,7 +2224,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.polite.normal[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.polite[1]</t>
+          <t xml:space="preserve">fateDefender.polite.normal[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2256,7 +2256,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2288,7 +2288,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2320,7 +2320,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.polite.normal[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.polite[1]</t>
+          <t xml:space="preserve">fateLoser.polite.normal[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2352,7 +2352,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.polite.normal[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.polite[1]</t>
+          <t xml:space="preserve">fateWinner.polite.normal[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2384,7 +2384,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.polite[1]</t>
+          <t xml:space="preserve">loser.polite.normal[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2416,7 +2416,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.polite[1]</t>
+          <t xml:space="preserve">winner.polite.normal[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2448,7 +2448,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2480,7 +2480,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.normal[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -3280,7 +3280,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.polite.normal[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.polite[1]</t>
+          <t xml:space="preserve">accepted.polite.normal[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3312,7 +3312,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.polite.normal[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.polite[1]</t>
+          <t xml:space="preserve">defended.polite.normal[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3344,7 +3344,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.polite.normal[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.polite[1]</t>
+          <t xml:space="preserve">defense_failed.polite.normal[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3376,7 +3376,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.polite.normal[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.polite[1]</t>
+          <t xml:space="preserve">former_champ.polite.normal[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3408,7 +3408,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.polite.normal[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.polite.normal[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3440,7 +3440,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.polite.normal[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.polite.normal[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3472,7 +3472,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.polite[1]</t>
+          <t xml:space="preserve">A1_champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3504,7 +3504,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.polite.normal[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.polite.normal[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3536,7 +3536,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.polite[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.polite.normal[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.polite[2]</t>
+          <t xml:space="preserve">A2_uncrowned.polite.normal[2]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3568,7 +3568,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.polite.normal[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.polite[1]</t>
+          <t xml:space="preserve">A3_heel.polite.normal[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3600,7 +3600,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.polite[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.polite.normal[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.polite[2]</t>
+          <t xml:space="preserve">A3_heel.polite.normal[2]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3632,7 +3632,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.polite.normal[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.polite.normal[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3664,7 +3664,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.polite[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.polite.normal[2]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.polite[2]</t>
+          <t xml:space="preserve">A4_veteran.polite.normal[2]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3696,7 +3696,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.polite.normal[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.polite[1]</t>
+          <t xml:space="preserve">B1_young.polite.normal[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3728,7 +3728,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.polite[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.polite.normal[2]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.polite[2]</t>
+          <t xml:space="preserve">B1_young.polite.normal[2]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3760,7 +3760,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.polite.normal[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.polite[1]</t>
+          <t xml:space="preserve">B2_prime.polite.normal[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3792,7 +3792,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.polite[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.polite.normal[2]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.polite[2]</t>
+          <t xml:space="preserve">B2_prime.polite.normal[2]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3824,7 +3824,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.polite.normal[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.polite[1]</t>
+          <t xml:space="preserve">B3_older.polite.normal[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3856,7 +3856,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.polite[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.polite.normal[2]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.polite[2]</t>
+          <t xml:space="preserve">B3_older.polite.normal[2]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3888,7 +3888,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3920,7 +3920,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.polite[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.polite[2]</t>
+          <t xml:space="preserve">B4_champion_injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3952,7 +3952,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3984,7 +3984,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.polite[1]</t>
+          <t xml:space="preserve">raise_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -4016,7 +4016,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -4048,7 +4048,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4080,7 +4080,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.polite[1]</t>
+          <t xml:space="preserve">raise_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4112,7 +4112,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4144,7 +4144,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4176,7 +4176,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.normal[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.polite[2]</t>
+          <t xml:space="preserve">sudden_departure.polite.normal[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4208,7 +4208,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.polite[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4240,7 +4240,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.polite[1]</t>
+          <t xml:space="preserve">transfer_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4272,7 +4272,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.normal[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.polite[2]</t>
+          <t xml:space="preserve">transfer_open.polite.normal[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4304,7 +4304,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.polite[1]</t>
+          <t xml:space="preserve">transfer_release.polite.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4336,7 +4336,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4368,7 +4368,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4400,7 +4400,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.polite[1]</t>
+          <t xml:space="preserve">start.polite.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4432,7 +4432,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4464,7 +4464,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4496,7 +4496,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4528,7 +4528,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.normal.polite[1]</t>
+          <t xml:space="preserve">fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4560,7 +4560,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.normal.polite[1]</t>
+          <t xml:space="preserve">heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4592,7 +4592,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.normal.polite[1]</t>
+          <t xml:space="preserve">warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4624,7 +4624,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.polite[1]</t>
+          <t xml:space="preserve">cap_reached.polite.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4656,7 +4656,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.polite[1]</t>
+          <t xml:space="preserve">ovr_elite.polite.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4688,7 +4688,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.polite[1]</t>
+          <t xml:space="preserve">ovr_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4720,7 +4720,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.polite[1]</t>
+          <t xml:space="preserve">ovr_legend.polite.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4752,7 +4752,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.polite[1]</t>
+          <t xml:space="preserve">pop_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4784,7 +4784,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.polite[1]</t>
+          <t xml:space="preserve">pop_star.polite.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4816,7 +4816,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4848,7 +4848,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4880,7 +4880,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4912,7 +4912,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.polite[1]</t>
+          <t xml:space="preserve">defeat.polite.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4944,7 +4944,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.polite[1]</t>
+          <t xml:space="preserve">bestMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4976,7 +4976,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.polite[1]</t>
+          <t xml:space="preserve">champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -5008,7 +5008,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.polite[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -5040,7 +5040,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.polite[1]</t>
+          <t xml:space="preserve">mediaAward.polite.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5072,7 +5072,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.polite[1]</t>
+          <t xml:space="preserve">mvp.polite.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5104,7 +5104,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5136,7 +5136,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5168,7 +5168,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5200,7 +5200,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5232,7 +5232,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5264,7 +5264,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.polite[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[3]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5296,7 +5296,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.polite[1]</t>
+          <t xml:space="preserve">special_treatment.polite.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5328,7 +5328,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.polite[1]</t>
+          <t xml:space="preserve">E1.polite.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5360,7 +5360,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.polite[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.polite[2]</t>
+          <t xml:space="preserve">E1.polite.normal[2]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5392,7 +5392,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.normal.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.normal.polite[1]</t>
+          <t xml:space="preserve">E1.accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5424,7 +5424,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5456,7 +5456,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5488,7 +5488,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5520,7 +5520,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5552,7 +5552,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5584,7 +5584,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5616,7 +5616,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5648,7 +5648,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5680,7 +5680,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5712,7 +5712,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5744,7 +5744,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.polite[1]</t>
+          <t xml:space="preserve">draftInterest.polite.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5776,7 +5776,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.polite[2]</t>
+          <t xml:space="preserve">draftInterest.polite.normal[2]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5808,7 +5808,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.polite[1]</t>
+          <t xml:space="preserve">draftJoin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5840,7 +5840,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.polite[2]</t>
+          <t xml:space="preserve">draftJoin.polite.normal[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5872,7 +5872,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal.polite[1]</t>
+          <t xml:space="preserve">faGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5904,7 +5904,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.polite[1]</t>
+          <t xml:space="preserve">faSigning.polite.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5936,7 +5936,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.polite[2]</t>
+          <t xml:space="preserve">faSigning.polite.normal[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5968,7 +5968,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.polite[1]</t>
+          <t xml:space="preserve">faWelcome.polite.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -6000,7 +6000,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.polite[2]</t>
+          <t xml:space="preserve">faWelcome.polite.normal[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6032,7 +6032,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.normal.polite[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6064,7 +6064,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.normal.polite[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6096,7 +6096,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.normal.polite[1]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6128,7 +6128,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.polite[1]</t>
+          <t xml:space="preserve">injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6160,7 +6160,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.polite[2]</t>
+          <t xml:space="preserve">injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6192,7 +6192,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.polite[1]</t>
+          <t xml:space="preserve">release.polite.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6224,7 +6224,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.polite[2]</t>
+          <t xml:space="preserve">release.polite.normal[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6256,7 +6256,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.polite[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6288,7 +6288,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.polite[2]</t>
+          <t xml:space="preserve">rentalGreeting.polite.normal[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6320,7 +6320,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal.polite[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6352,7 +6352,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.polite[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6384,7 +6384,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.polite[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6416,7 +6416,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.polite[1]</t>
+          <t xml:space="preserve">titleDefense.polite.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6448,7 +6448,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.polite[2]</t>
+          <t xml:space="preserve">titleDefense.polite.normal[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6480,7 +6480,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.polite[1]</t>
+          <t xml:space="preserve">titleLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6512,7 +6512,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.polite[2]</t>
+          <t xml:space="preserve">titleLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6544,7 +6544,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.polite[1]</t>
+          <t xml:space="preserve">titleWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6576,7 +6576,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.polite[2]</t>
+          <t xml:space="preserve">titleWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6608,7 +6608,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6640,7 +6640,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6672,7 +6672,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6704,7 +6704,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6736,7 +6736,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6768,7 +6768,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6800,7 +6800,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6832,7 +6832,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6864,7 +6864,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6896,7 +6896,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6928,7 +6928,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6960,7 +6960,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -7344,7 +7344,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.polite[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7376,7 +7376,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.polite[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7408,7 +7408,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.polite[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7440,7 +7440,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.polite[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7472,7 +7472,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.polite[1]</t>
+          <t xml:space="preserve">GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7504,7 +7504,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.polite[1]</t>
+          <t xml:space="preserve">GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7536,7 +7536,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.polite[1]</t>
+          <t xml:space="preserve">GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7568,7 +7568,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.polite[1]</t>
+          <t xml:space="preserve">GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7600,7 +7600,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.polite[1]</t>
+          <t xml:space="preserve">GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7632,7 +7632,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.polite[1]</t>
+          <t xml:space="preserve">GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7664,7 +7664,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.polite[1]</t>
+          <t xml:space="preserve">GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7696,7 +7696,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.polite[1]</t>
+          <t xml:space="preserve">GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7728,7 +7728,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.polite[1]</t>
+          <t xml:space="preserve">GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7760,7 +7760,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.polite[1]</t>
+          <t xml:space="preserve">GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7792,7 +7792,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.polite[1]</t>
+          <t xml:space="preserve">GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7824,7 +7824,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7856,7 +7856,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7888,7 +7888,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.polite[2]</t>
+          <t xml:space="preserve">preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7920,7 +7920,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.polite[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.polite[3]</t>
+          <t xml:space="preserve">preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7952,7 +7952,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7984,7 +7984,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.polite[2]</t>
+          <t xml:space="preserve">preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -8016,7 +8016,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.polite[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.polite[3]</t>
+          <t xml:space="preserve">preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8048,7 +8048,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.polite[1]</t>
+          <t xml:space="preserve">survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8080,7 +8080,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.polite[2]</t>
+          <t xml:space="preserve">survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8112,7 +8112,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.polite[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.polite[3]</t>
+          <t xml:space="preserve">survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8144,7 +8144,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.polite[1]</t>
+          <t xml:space="preserve">champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8176,7 +8176,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.polite[2]</t>
+          <t xml:space="preserve">champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8208,7 +8208,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.polite[1]</t>
+          <t xml:space="preserve">defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8240,7 +8240,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.polite[2]</t>
+          <t xml:space="preserve">defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8272,7 +8272,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.polite[1]</t>
+          <t xml:space="preserve">gauntlet.polite.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8304,7 +8304,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.polite[2]</t>
+          <t xml:space="preserve">gauntlet.polite.normal[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8336,7 +8336,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8368,7 +8368,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8400,7 +8400,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8432,7 +8432,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal.polite[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.polite[1]</t>
+          <t xml:space="preserve">fighter.polite.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8464,7 +8464,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8496,7 +8496,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.polite[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(丁寧×ノーマル)に該当するキャラクター: 9名</t>
+          <t xml:space="preserve">このタイプ(丁寧×ノーマル)に該当するキャラクター: 8名</t>
         </is>
       </c>
     </row>
@@ -301,7 +301,7 @@
     <row r="7">
       <c r="A7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">穴澤ほのか</t>
+          <t xml:space="preserve">玉手すみれ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -316,14 +316,14 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ファンサービス、引き出し上手、野心</t>
+          <t xml:space="preserve">ヒール適性、威圧感、華</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">玉手すみれ</t>
+          <t xml:space="preserve">松久保伊織</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -333,24 +333,24 @@
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Neutral</t>
+          <t xml:space="preserve">Babyface</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ヒール適性、威圧感、華</t>
+          <t xml:space="preserve">忠誠心、早熟</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">松久保伊織</t>
+          <t xml:space="preserve">米山杏里</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grappler</t>
+          <t xml:space="preserve">Allround</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
@@ -360,19 +360,19 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">忠誠心、早熟</t>
+          <t xml:space="preserve">ガラスの身体、リーダー気質、人望、引き出し上手</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">米山杏里</t>
+          <t xml:space="preserve">土岐山乃ノ佳</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Allround</t>
+          <t xml:space="preserve">Aerial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
@@ -382,49 +382,27 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ガラスの身体、リーダー気質、人望、引き出し上手</t>
+          <t xml:space="preserve">努力家</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">土岐山乃ノ佳</t>
+          <t xml:space="preserve">結城玲奈</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Aerial</t>
+          <t xml:space="preserve">Allround</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Babyface</t>
+          <t xml:space="preserve">Neutral</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">努力家</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">結城玲奈</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Allround</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Neutral</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">努力家</t>
         </is>
@@ -438,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -553,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだです!</t>
+          <t xml:space="preserve">まだまだです！</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2707,7 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます! ……行ってまいります。</t>
+          <t xml:space="preserve">ありがとうございます！ ……行ってまいります。</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2835,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました! ……見ていてくださいましたか。</t>
+          <t xml:space="preserve">やりました！ ……見ていてくださいましたか。</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3091,7 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの力が及びませんでした。お見事です。</t>
+          <t xml:space="preserve">私の力が及びませんでした。お見事です。</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3219,7 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はわたしが上でしたね。お強かったですよ。</t>
+          <t xml:space="preserve">今日は私が上でしたね。お強かったですよ。</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3603,7 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしがいなくなれば、寂しくなりますよ</t>
+          <t xml:space="preserve">私がいなくなれば、寂しくなりますよ</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3635,7 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが、わたしの全部でした</t>
+          <t xml:space="preserve">ここが、私の全部でした</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3731,7 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの物語は…こんなところで終わりなのでしょうか…</t>
+          <t xml:space="preserve">私の物語は…こんなところで終わりなのでしょうか…</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3955,7 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残らせていただきます。ここが、わたくしの居場所ですから</t>
+          <t xml:space="preserve">残らせていただきます。ここが、私の居場所ですから</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4922,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4959,7 +4937,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4969,14 +4947,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でした。…相手に感謝しています</t>
+          <t xml:space="preserve">団体を代表して戦えたこと、そして勝てたことを誇りに思います。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4991,7 +4969,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[1]</t>
+          <t xml:space="preserve">bestMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -5001,14 +4979,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間、ベルトを守り続けることができました。支えてくださった皆さんに感謝します</t>
+          <t xml:space="preserve">最高の試合でした。…相手に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -5023,7 +5001,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.normal[1]</t>
+          <t xml:space="preserve">champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -5033,14 +5011,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入り…夢のようです。支えてくださった全ての方に感謝いたします</t>
+          <t xml:space="preserve">一年間、ベルトを守り続けることができました。支えてくださった皆さんに感謝します</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5055,7 +5033,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.polite.normal[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5065,14 +5043,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余る光栄です。ありがとうございます</t>
+          <t xml:space="preserve">殿堂入り…夢のようです。支えてくださった全ての方に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5087,7 +5065,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.normal[1]</t>
+          <t xml:space="preserve">mediaAward.polite.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5097,14 +5075,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPをいただけるとは…ありがとうございます。来年も頑張ります</t>
+          <t xml:space="preserve">身に余る光栄です。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5114,12 +5092,12 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">mvp.polite.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5129,14 +5107,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで試合ができるなんて、本当に感謝しています</t>
+          <t xml:space="preserve">MVPをいただけるとは…ありがとうございます。来年も頑張ります</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5146,12 +5124,12 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">springTagChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5161,14 +5139,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日を迎えられて、光栄です</t>
+          <t xml:space="preserve">相棒と力を合わせた成果です。皆さま、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5183,7 +5161,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[3]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5193,14 +5171,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くさせていただきます</t>
+          <t xml:space="preserve">ドームで試合ができるなんて、本当に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5210,12 +5188,12 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5225,14 +5203,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に感謝しかありません</t>
+          <t xml:space="preserve">今日という日を迎えられて、光栄です</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5242,12 +5220,12 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5257,14 +5235,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます</t>
+          <t xml:space="preserve">全力を尽くさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5279,7 +5257,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[3]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5289,14 +5267,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩は、これからの試合で返します</t>
+          <t xml:space="preserve">満員のお客様に感謝しかありません</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5306,29 +5284,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご丁寧な治療を…ありがとうございます。一日でも早く戻ります</t>
+          <t xml:space="preserve">社長、本当にありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5338,29 +5316,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演のお話をいただきまして…ご検討いただけますでしょうか</t>
+          <t xml:space="preserve">この恩は、これからの試合で返します</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5370,12 +5348,12 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.normal[2]</t>
+          <t xml:space="preserve">special_treatment.polite.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5385,14 +5363,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出演のお話をいただきました。ぜひ、やらせていただきたいです</t>
+          <t xml:space="preserve">ご丁寧な治療を…ありがとうございます。一日でも早く戻ります</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5402,12 +5380,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.polite.normal[1]</t>
+          <t xml:space="preserve">E1.polite.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5417,14 +5395,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました……!夢みたいです、本当にありがとうございます</t>
+          <t xml:space="preserve">メディア出演のお話をいただきまして…ご検討いただけますでしょうか</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5434,29 +5412,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">E1.polite.normal[2]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
+          <t xml:space="preserve">出演のお話をいただきました。ぜひ、やらせていただきたいです</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5466,29 +5444,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">E1.accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
+          <t xml:space="preserve">やりました……！夢みたいです、本当にありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5498,7 +5476,7 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
@@ -5513,14 +5491,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日はよろしくお願いいたします</t>
+          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5530,7 +5508,7 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
@@ -5545,14 +5523,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
+          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5562,7 +5540,7 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
@@ -5577,14 +5555,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
+          <t xml:space="preserve">本日はよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5594,7 +5572,7 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
@@ -5609,14 +5587,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5626,7 +5604,7 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
@@ -5641,14 +5619,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
+          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5658,7 +5636,7 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
@@ -5673,14 +5651,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
+          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5690,7 +5668,7 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
@@ -5705,14 +5683,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
+          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5722,7 +5700,7 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
@@ -5737,14 +5715,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
+          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5754,12 +5732,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5769,14 +5747,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
+          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5786,12 +5764,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5801,14 +5779,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
+          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5823,7 +5801,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.normal[1]</t>
+          <t xml:space="preserve">draftInterest.polite.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5833,14 +5811,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日はよろしくお願いいたします</t>
+          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5855,7 +5833,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.normal[2]</t>
+          <t xml:space="preserve">draftInterest.polite.normal[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5865,14 +5843,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
+          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5887,7 +5865,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">draftJoin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5897,14 +5875,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾っていただいた御恩は、試合でお返しします</t>
+          <t xml:space="preserve">本日はよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5919,7 +5897,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.normal[1]</t>
+          <t xml:space="preserve">draftJoin.polite.normal[2]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5929,14 +5907,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5951,7 +5929,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.normal[2]</t>
+          <t xml:space="preserve">faGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5961,14 +5939,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
+          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5983,7 +5961,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.normal[1]</t>
+          <t xml:space="preserve">faSigning.polite.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5993,14 +5971,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
+          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -6015,7 +5993,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.normal[2]</t>
+          <t xml:space="preserve">faSigning.polite.normal[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6025,14 +6003,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
+          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6047,7 +6025,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.polite.normal[1]</t>
+          <t xml:space="preserve">faWelcome.polite.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6057,14 +6035,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
+          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6079,7 +6057,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.polite.normal[1]</t>
+          <t xml:space="preserve">faWelcome.polite.normal[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6089,14 +6067,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
+          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6111,7 +6089,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.polite.normal[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6121,14 +6099,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
+          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6143,7 +6121,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.normal[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6153,14 +6131,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
+          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6175,7 +6153,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.normal[2]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6185,14 +6163,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
+          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6207,7 +6185,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.normal[1]</t>
+          <t xml:space="preserve">injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6217,14 +6195,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
+          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6239,7 +6217,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.normal[2]</t>
+          <t xml:space="preserve">injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6249,14 +6227,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
+          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6271,7 +6249,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">release.polite.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6281,14 +6259,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
+          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6303,7 +6281,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.normal[2]</t>
+          <t xml:space="preserve">release.polite.normal[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6313,14 +6291,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6335,7 +6313,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6345,14 +6323,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
+          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6367,7 +6345,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.normal[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6377,14 +6355,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6399,7 +6377,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.normal[2]</t>
+          <t xml:space="preserve">scoutGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6409,14 +6387,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
+          <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6431,7 +6409,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6441,14 +6419,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
+          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6463,7 +6441,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.normal[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6473,14 +6451,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
+          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6495,7 +6473,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.normal[1]</t>
+          <t xml:space="preserve">titleDefense.polite.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6505,14 +6483,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
+          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6527,7 +6505,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.normal[2]</t>
+          <t xml:space="preserve">titleDefense.polite.normal[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6537,14 +6515,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6559,7 +6537,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.normal[1]</t>
+          <t xml:space="preserve">titleLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6569,14 +6547,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
+          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6591,7 +6569,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.normal[2]</t>
+          <t xml:space="preserve">titleLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6601,14 +6579,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
+          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6618,12 +6596,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">titleWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6633,14 +6611,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
+          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6650,12 +6628,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">titleWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6665,14 +6643,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
+          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6682,7 +6660,7 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
@@ -6697,14 +6675,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
+          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6714,7 +6692,7 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
@@ -6729,14 +6707,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6746,7 +6724,7 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
@@ -6761,14 +6739,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
+          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6778,7 +6756,7 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
@@ -6793,14 +6771,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6810,7 +6788,7 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
@@ -6825,14 +6803,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
+          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6842,7 +6820,7 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
@@ -6857,14 +6835,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
+          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6874,7 +6852,7 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
@@ -6889,14 +6867,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
+          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6906,7 +6884,7 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
@@ -6921,14 +6899,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6938,7 +6916,7 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
@@ -6953,14 +6931,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
+          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6970,7 +6948,7 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
@@ -6985,14 +6963,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
+          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -7002,29 +6980,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう以前のようには…すみません</t>
+          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7034,29 +7012,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し壁ができたようで…気のせいだといいんですが</t>
+          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7071,7 +7049,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7081,14 +7059,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると自然体でいられます。ありがたいです</t>
+          <t xml:space="preserve">もう以前のようには…すみません</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7103,7 +7081,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7113,14 +7091,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なくてはならない方です。心からそう思います</t>
+          <t xml:space="preserve">少し壁ができたようで…気のせいだといいんですが</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7135,7 +7113,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7145,14 +7123,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も、穏やかになってきました</t>
+          <t xml:space="preserve">一緒にいると自然体でいられます。ありがたいです</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7167,7 +7145,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7177,14 +7155,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても負けたくないんです…この気持ちは…</t>
+          <t xml:space="preserve">なくてはならない方です。心からそう思います</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7199,7 +7177,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7209,14 +7187,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けるわけにはいきません</t>
+          <t xml:space="preserve">関係も、穏やかになってきました</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7231,7 +7209,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7241,14 +7219,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いが…私のプロレス人生そのものです</t>
+          <t xml:space="preserve">どうしても負けたくないんです…この気持ちは…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7263,7 +7241,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7273,14 +7251,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の一員でいられて…本当に幸せです</t>
+          <t xml:space="preserve">絶対に負けるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7295,7 +7273,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7305,14 +7283,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すみません。もう限界かもしれません</t>
+          <t xml:space="preserve">この戦いが…私のプロレス人生そのものです</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.polite[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7327,7 +7305,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.polite[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7337,14 +7315,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…少し不安になってきました…</t>
+          <t xml:space="preserve">この団体の一員でいられて…本当に幸せです</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.polite[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7354,12 +7332,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.polite.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.polite[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7369,14 +7347,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたが…良い試合ができたと思います</t>
+          <t xml:space="preserve">…すみません。もう限界かもしれません</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.polite[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7386,12 +7364,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.polite.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.polite[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7401,14 +7379,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
+          <t xml:space="preserve">すみません…少し不安になってきました…</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7423,7 +7401,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7433,14 +7411,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
+          <t xml:space="preserve">負けてしまいましたが…良い試合ができたと思います</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7455,7 +7433,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7465,14 +7443,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。応援のおかげです</t>
+          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7487,7 +7465,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7497,14 +7475,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
+          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7519,7 +7497,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7529,14 +7507,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し寂しいというか…不安が…</t>
+          <t xml:space="preserve">勝てました。応援のおかげです</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7551,7 +7529,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.polite.normal[1]</t>
+          <t xml:space="preserve">GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7561,14 +7539,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
+          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7583,7 +7561,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7593,14 +7571,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると安心します</t>
+          <t xml:space="preserve">少し寂しいというか…不安が…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7615,7 +7593,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7625,14 +7603,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">活躍が気になってしまいます</t>
+          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7647,7 +7625,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.normal[1]</t>
+          <t xml:space="preserve">GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7657,14 +7635,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
+          <t xml:space="preserve">一緒にいると安心します</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7679,7 +7657,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.normal[1]</t>
+          <t xml:space="preserve">GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7689,14 +7667,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
+          <t xml:space="preserve">活躍が気になってしまいます</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7711,7 +7689,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.normal[1]</t>
+          <t xml:space="preserve">GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7721,14 +7699,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
+          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7743,7 +7721,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.normal[1]</t>
+          <t xml:space="preserve">GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7753,14 +7731,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
+          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7775,7 +7753,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.normal[1]</t>
+          <t xml:space="preserve">GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7785,14 +7763,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
+          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7807,7 +7785,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.polite.normal[1]</t>
+          <t xml:space="preserve">GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7817,14 +7795,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
+          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7834,12 +7812,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7849,14 +7827,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
+          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7866,29 +7844,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[1]</t>
+          <t xml:space="preserve">GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
+          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7898,29 +7876,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7935,7 +7913,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[3]</t>
+          <t xml:space="preserve">preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7945,14 +7923,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
+          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7967,7 +7945,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[1]</t>
+          <t xml:space="preserve">preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7977,14 +7955,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
+          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7999,7 +7977,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[2]</t>
+          <t xml:space="preserve">preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -8009,14 +7987,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
+          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8031,7 +8009,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[3]</t>
+          <t xml:space="preserve">preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8041,14 +8019,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
+          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8063,7 +8041,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[1]</t>
+          <t xml:space="preserve">preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8073,14 +8051,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8095,7 +8073,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[2]</t>
+          <t xml:space="preserve">preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8105,14 +8083,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
+          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8127,7 +8105,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[3]</t>
+          <t xml:space="preserve">survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8137,14 +8115,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
+          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8154,12 +8132,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[1]</t>
+          <t xml:space="preserve">survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8169,14 +8147,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8186,12 +8164,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[2]</t>
+          <t xml:space="preserve">survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8201,14 +8179,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8223,7 +8201,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.normal[1]</t>
+          <t xml:space="preserve">champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8233,14 +8211,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
+          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8255,7 +8233,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.normal[2]</t>
+          <t xml:space="preserve">champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8265,14 +8243,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
+          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8287,7 +8265,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.normal[1]</t>
+          <t xml:space="preserve">defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8297,14 +8275,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
+          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8319,7 +8297,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.normal[2]</t>
+          <t xml:space="preserve">defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8329,14 +8307,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
+          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8346,12 +8324,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">gauntlet.polite.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8361,14 +8339,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
+          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8378,12 +8356,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">gauntlet.polite.normal[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8393,14 +8371,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
+          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8410,7 +8388,7 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
@@ -8425,14 +8403,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
+          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8442,29 +8420,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで走り切れました。…ありがとうございました</t>
+          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8474,7 +8452,7 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
@@ -8484,49 +8462,113 @@
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾っていただいた御恩は、試合でお返しします</t>
+          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで走り切れました。…ありがとうございました</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr" s="2">
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr" s="12">
+      <c r="D254" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr" s="2">
+      <c r="E254" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr" s="3">
+      <c r="F254" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H252"/>
+  <autoFilter ref="A1:H254"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H261"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3962,7 +3962,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.polite.normal[1]</t>
+          <t xml:space="preserve">decline_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3987,14 +3987,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。今後とも、どうぞよろしくお願いいたします。</t>
+          <t xml:space="preserve">はい、その額で。落ちたぶんは、来年の宿題ということにしておきますね。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.polite.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.polite.normal[1]</t>
+          <t xml:space="preserve">decline_hold.polite.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -4019,14 +4019,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上げていただけるのなら、ありがたいです。頑張りますね。</t>
+          <t xml:space="preserve">えっ……いいんですか、それ。……ずるいですよ、そんなふうにされたら、休めなくなるじゃないですか。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.polite.normal[1]</t>
+          <t xml:space="preserve">decline_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4051,14 +4051,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうですか。かしこまりました。</t>
+          <t xml:space="preserve">……そうですか。去年より動けていないのは、自分がいちばん分かっていますから。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.polite.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.polite.normal[1]</t>
+          <t xml:space="preserve">decline_strict.polite.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4083,14 +4083,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。前向きに検討させていただきます</t>
+          <t xml:space="preserve">……そこまでやりますか。ええ、分かりました。恨みませんけど、覚えてはおきますね。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.polite.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうですか。承知いたしました。……少し残念ですけれど。</t>
+          <t xml:space="preserve">ええ、それでいいんです。変に気を遣われるより、こう扱ってもらえるほうが助かります。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.polite.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.polite.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4147,14 +4147,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、手短に申し上げます。退団させていただきます。もう決めました。</t>
+          <t xml:space="preserve">……据え置き、ですか。こっちが言い出したのに、話がまとまりませんね。……ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.normal[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4179,14 +4179,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。ですが、もうここでは続けられません。</t>
+          <t xml:space="preserve">社長、先に言わせてください。もう全盛期じゃありません。査定は、そのぶん下げてもらって結構です。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.polite.normal[1]</t>
+          <t xml:space="preserve">raise_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4211,14 +4211,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくださるんですね。{record}正直、新しい場所で挑戦してみたいんです。</t>
+          <t xml:space="preserve">ありがとうございます。今後とも、どうぞよろしくお願いいたします。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お話があります。{tenure}この団体を離れようと考えております。</t>
+          <t xml:space="preserve">上げていただけるのなら、ありがたいです。頑張りますね。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.normal[2]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4275,14 +4275,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}色々と考えたのですが……別の環境でやってみたいのです。</t>
+          <t xml:space="preserve">……そうですか。かしこまりました。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.polite.normal[1]</t>
+          <t xml:space="preserve">raise_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知しました。{tenure_farewell}{rivalry}お世話になりました。</t>
+          <t xml:space="preserve">ありがとうございます。前向きに検討させていただきます</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.polite.normal[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがたいのですが……もう、決めたことなんです。申し訳ありません。</t>
+          <t xml:space="preserve">……そうですか。承知いたしました。……少し残念ですけれど。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.polite.normal[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまでしてくださるんですね。……分かりました。もう少し頑張ってみます。</t>
+          <t xml:space="preserve">社長、手短に申し上げます。退団させていただきます。もう決めました。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.normal[2]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.polite.normal[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.normal[2]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4403,46 +4403,46 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残りたい気持ちはあります。…条件を聞かせてください</t>
+          <t xml:space="preserve">お世話になりました。ですが、もうここでは続けられません。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼ながら、意見を申し上げさせてください。</t>
+          <t xml:space="preserve">聞いてくださるんですね。{record}正直、新しい場所で挑戦してみたいんです。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4452,29 +4452,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">transfer_open.polite.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが変わった気がします。…成長できている実感があります</t>
+          <t xml:space="preserve">社長、お話があります。{tenure}この団体を離れようと考えております。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.normal[2]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4484,29 +4484,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">transfer_open.polite.normal[2]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが掴めそうな気がします。もう少しで…</t>
+          <t xml:space="preserve">社長。{tenure}色々と考えたのですが……別の環境でやってみたいのです。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4516,29 +4516,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.polite.normal[1]</t>
+          <t xml:space="preserve">transfer_release.polite.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
+          <t xml:space="preserve">……承知しました。{tenure_farewell}{rivalry}お世話になりました。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4548,29 +4548,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.polite.normal[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
+          <t xml:space="preserve">……ありがたいのですが……もう、決めたことなんです。申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4580,29 +4580,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.polite.normal[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
+          <t xml:space="preserve">……そこまでしてくださるんですね。……分かりました。もう少し頑張ってみます。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.normal[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4612,61 +4612,61 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.polite.normal[1]</t>
+          <t xml:space="preserve">start.polite.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られただけで、幸せです</t>
+          <t xml:space="preserve">残りたい気持ちはあります。…条件を聞かせてください</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.normal[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、皆さんのおかげです</t>
+          <t xml:space="preserve">失礼ながら、意見を申し上げさせてください。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.normal[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4691,14 +4691,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しずつですが、成長を実感しています</t>
+          <t xml:space="preserve">何かが変わった気がします。…成長できている実感があります</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.normal[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この場所に立たせていただけるなんて…身に余る光栄です</t>
+          <t xml:space="preserve">何かが掴めそうな気がします。もう少しで…</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.polite.normal[1]</t>
+          <t xml:space="preserve">fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4755,14 +4755,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださる方が増えて、嬉しいです</t>
+          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.polite.normal[1]</t>
+          <t xml:space="preserve">heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4787,14 +4787,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに多くの方に応援いただいて…感謝の気持ちでいっぱいです</t>
+          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…何のために戦っているのか、わからなくなってきました</t>
+          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">cap_reached.polite.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4851,14 +4851,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…戦う理由を思い出しました</t>
+          <t xml:space="preserve">ここまで来られただけで、幸せです</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">ovr_elite.polite.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4883,14 +4883,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…調子が戻ってきた気がします</t>
+          <t xml:space="preserve">ここまで来られたのは、皆さんのおかげです</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.polite.normal[1]</t>
+          <t xml:space="preserve">ovr_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4915,14 +4915,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、何をやってもうまくいかなくて…</t>
+          <t xml:space="preserve">少しずつですが、成長を実感しています</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4932,29 +4932,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.polite.normal[1]</t>
+          <t xml:space="preserve">ovr_legend.polite.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体を代表して戦えたこと、そして勝てたことを誇りに思います。</t>
+          <t xml:space="preserve">この場所に立たせていただけるなんて…身に余る光栄です</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4964,29 +4964,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.normal[1]</t>
+          <t xml:space="preserve">pop_growth.polite.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でした。…相手に感謝しています</t>
+          <t xml:space="preserve">応援してくださる方が増えて、嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4996,29 +4996,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[1]</t>
+          <t xml:space="preserve">pop_star.polite.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間、ベルトを守り続けることができました。支えてくださった皆さんに感謝します</t>
+          <t xml:space="preserve">こんなに多くの方に応援いただいて…感謝の気持ちでいっぱいです</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5028,29 +5028,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入り…夢のようです。支えてくださった全ての方に感謝いたします</t>
+          <t xml:space="preserve">最近…何のために戦っているのか、わからなくなってきました</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余る光栄です。ありがとうございます</t>
+          <t xml:space="preserve">ようやく…戦う理由を思い出しました</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.normal[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5092,29 +5092,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPをいただけるとは…ありがとうございます。来年も頑張ります</t>
+          <t xml:space="preserve">ようやく…調子が戻ってきた気がします</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5124,29 +5124,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.polite.normal[1]</t>
+          <t xml:space="preserve">defeat.polite.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒と力を合わせた成果です。皆さま、ありがとうございます。</t>
+          <t xml:space="preserve">最近、何をやってもうまくいかなくて…</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5171,14 +5171,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで試合ができるなんて、本当に感謝しています</t>
+          <t xml:space="preserve">団体を代表して戦えたこと、そして勝てたことを誇りに思います。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">bestMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5203,14 +5203,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日を迎えられて、光栄です</t>
+          <t xml:space="preserve">最高の試合でした。…相手に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[3]</t>
+          <t xml:space="preserve">champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5235,14 +5235,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くさせていただきます</t>
+          <t xml:space="preserve">一年間、ベルトを守り続けることができました。支えてくださった皆さんに感謝します</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に感謝しかありません</t>
+          <t xml:space="preserve">殿堂入り…夢のようです。支えてくださった全ての方に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.polite.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">mediaAward.polite.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5299,14 +5299,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます</t>
+          <t xml:space="preserve">身に余る光栄です。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[3]</t>
+          <t xml:space="preserve">mvp.polite.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5331,14 +5331,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩は、これからの試合で返します</t>
+          <t xml:space="preserve">MVPをいただけるとは…ありがとうございます。来年も頑張ります</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5348,29 +5348,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.polite.normal[1]</t>
+          <t xml:space="preserve">springTagChampion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご丁寧な治療を…ありがとうございます。一日でも早く戻ります</t>
+          <t xml:space="preserve">相棒と力を合わせた成果です。皆さま、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5380,29 +5380,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア出演のお話をいただきまして…ご検討いただけますでしょうか</t>
+          <t xml:space="preserve">ドームで試合ができるなんて、本当に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5412,29 +5412,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出演のお話をいただきました。ぜひ、やらせていただきたいです</t>
+          <t xml:space="preserve">今日という日を迎えられて、光栄です</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5444,29 +5444,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました……！夢みたいです、本当にありがとうございます</t>
+          <t xml:space="preserve">全力を尽くさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
@@ -5486,19 +5486,19 @@
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
+          <t xml:space="preserve">満員のお客様に感謝しかありません</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
@@ -5518,19 +5518,19 @@
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
+          <t xml:space="preserve">社長、本当にありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.normal[3]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5540,29 +5540,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[3]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日はよろしくお願いいたします</t>
+          <t xml:space="preserve">この恩は、これからの試合で返します</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5572,29 +5572,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">special_treatment.polite.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
+          <t xml:space="preserve">ご丁寧な治療を…ありがとうございます。一日でも早く戻ります</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5604,29 +5604,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">E1.polite.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
+          <t xml:space="preserve">メディア出演のお話をいただきまして…ご検討いただけますでしょうか</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5636,29 +5636,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">E1.polite.normal[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
+          <t xml:space="preserve">出演のお話をいただきました。ぜひ、やらせていただきたいです</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5668,29 +5668,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">E1.accept.polite.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
+          <t xml:space="preserve">やりました……！夢みたいです、本当にありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5715,14 +5715,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
+          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5747,14 +5747,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
+          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5779,14 +5779,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
+          <t xml:space="preserve">本日はよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5811,14 +5811,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5843,14 +5843,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
+          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5875,14 +5875,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日はよろしくお願いいたします</t>
+          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5907,14 +5907,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
+          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5939,14 +5939,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
+          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5971,14 +5971,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
+          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6003,14 +6003,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
+          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.normal[1]</t>
+          <t xml:space="preserve">draftInterest.polite.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
+          <t xml:space="preserve">よろしくお願いいたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.normal[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.normal[2]</t>
+          <t xml:space="preserve">draftInterest.polite.normal[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6067,14 +6067,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
+          <t xml:space="preserve">選んでいただけましたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.polite.normal[1]</t>
+          <t xml:space="preserve">draftJoin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6099,14 +6099,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
+          <t xml:space="preserve">本日はよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.normal[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.polite.normal[1]</t>
+          <t xml:space="preserve">draftJoin.polite.normal[2]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.polite.normal[1]</t>
+          <t xml:space="preserve">faGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6163,14 +6163,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
+          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.normal[1]</t>
+          <t xml:space="preserve">faSigning.polite.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6195,14 +6195,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
+          <t xml:space="preserve">よろしくお願いいたします。お力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.normal[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.normal[2]</t>
+          <t xml:space="preserve">faSigning.polite.normal[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6227,14 +6227,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
+          <t xml:space="preserve">新しい環境ですね…悪くありません。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.normal[1]</t>
+          <t xml:space="preserve">faWelcome.polite.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6259,14 +6259,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
+          <t xml:space="preserve">よろしくお願いいたします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.normal[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.normal[2]</t>
+          <t xml:space="preserve">faWelcome.polite.normal[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
+          <t xml:space="preserve">お力になれるよう、精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6323,14 +6323,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
+          <t xml:space="preserve">体が軽いんです。今なら、いくらでもやれます</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.normal[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
+          <t xml:space="preserve">正直、体が重いです。汗をかいた実感しかなくて</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.normal[1]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6387,14 +6387,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
+          <t xml:space="preserve">動けてはいます。ただ、手応えが少し薄くて</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.normal[1]</t>
+          <t xml:space="preserve">injury.polite.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6419,14 +6419,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
+          <t xml:space="preserve">ご迷惑をおかけします…しばらく休みます</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.normal[2]</t>
+          <t xml:space="preserve">injury.polite.normal[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6451,14 +6451,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
+          <t xml:space="preserve">すみません…万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.normal[1]</t>
+          <t xml:space="preserve">release.polite.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
+          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.normal[2]</t>
+          <t xml:space="preserve">release.polite.normal[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6547,14 +6547,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
+          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.normal[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.polite.normal[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6611,14 +6611,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
+          <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.normal[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6643,14 +6643,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
+          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
+          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">titleDefense.polite.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6707,14 +6707,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
+          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.normal[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">titleDefense.polite.normal[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6739,14 +6739,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">titleLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
+          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">titleLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6803,14 +6803,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
+          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">titleWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6835,14 +6835,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
+          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">titleWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6867,14 +6867,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
+          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6899,14 +6899,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
+          <t xml:space="preserve">お世話になりました。本当にありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6916,12 +6916,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6931,14 +6931,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6963,14 +6963,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
+          <t xml:space="preserve">レンタルですが、手は抜きません。よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6995,14 +6995,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7027,14 +7027,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
+          <t xml:space="preserve">悔しいです…。でも、いい経験になりました。次こそは</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7044,29 +7044,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう以前のようには…すみません</t>
+          <t xml:space="preserve">まだ実力が足りませんでした…もっと強くなって帰ってきます</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7076,29 +7076,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し壁ができたようで…気のせいだといいんですが</t>
+          <t xml:space="preserve">防衛できました…ほっとしています。でも、もっと強くならないと</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7108,29 +7108,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると自然体でいられます。ありがたいです</t>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7140,29 +7140,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なくてはならない方です。心からそう思います</t>
+          <t xml:space="preserve">ベルトを失ってしまいました…。でも、この団体で戦い続けます</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7172,29 +7172,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も、穏やかになってきました</t>
+          <t xml:space="preserve">…悔しいです。チャンピオンとして、もっとやれたはずなのに</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7204,29 +7204,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても負けたくないんです…この気持ちは…</t>
+          <t xml:space="preserve">やりました…！チャンピオンになれました…！夢のようです</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.normal[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7236,29 +7236,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.polite[1]</t>
+          <t xml:space="preserve">polite.normal[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けるわけにはいきません</t>
+          <t xml:space="preserve">このベルト、絶対に手放しません。応援ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7283,14 +7283,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いが…私のプロレス人生そのものです</t>
+          <t xml:space="preserve">もう以前のようには…すみません</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7315,14 +7315,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の一員でいられて…本当に幸せです</t>
+          <t xml:space="preserve">少し壁ができたようで…気のせいだといいんですが</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7347,14 +7347,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すみません。もう限界かもしれません</t>
+          <t xml:space="preserve">一緒にいると自然体でいられます。ありがたいです</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7379,14 +7379,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…少し不安になってきました…</t>
+          <t xml:space="preserve">なくてはならない方です。心からそう思います</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.polite.normal[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.polite[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7411,14 +7411,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたが…良い試合ができたと思います</t>
+          <t xml:space="preserve">関係も、穏やかになってきました</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.polite.normal[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7443,14 +7443,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
+          <t xml:space="preserve">どうしても負けたくないんです…この気持ちは…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.normal[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7475,14 +7475,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
+          <t xml:space="preserve">絶対に負けるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.normal[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.polite[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7507,14 +7507,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。応援のおかげです</t>
+          <t xml:space="preserve">この戦いが…私のプロレス人生そのものです</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.polite[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.normal[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.polite[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
+          <t xml:space="preserve">この団体の一員でいられて…本当に幸せです</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.polite[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.polite.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.polite[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7571,14 +7571,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し寂しいというか…不安が…</t>
+          <t xml:space="preserve">…すみません。もう限界かもしれません</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.polite[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.polite.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.polite[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7603,14 +7603,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
+          <t xml:space="preserve">すみません…少し不安になってきました…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7635,14 +7635,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると安心します</t>
+          <t xml:space="preserve">負けてしまいましたが…良い試合ができたと思います</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7667,14 +7667,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">活躍が気になってしまいます</t>
+          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7699,14 +7699,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
+          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7731,14 +7731,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
+          <t xml:space="preserve">勝てました。応援のおかげです</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.normal[1]</t>
+          <t xml:space="preserve">GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7763,14 +7763,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
+          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7795,14 +7795,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
+          <t xml:space="preserve">少し寂しいというか…不安が…</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7827,14 +7827,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
+          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.polite.normal[1]</t>
+          <t xml:space="preserve">GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
+          <t xml:space="preserve">一緒にいると安心します</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7891,14 +7891,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
+          <t xml:space="preserve">活躍が気になってしまいます</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7908,29 +7908,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[1]</t>
+          <t xml:space="preserve">GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
+          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7940,29 +7940,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[2]</t>
+          <t xml:space="preserve">GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7972,29 +7972,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[3]</t>
+          <t xml:space="preserve">GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
+          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8004,29 +8004,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[1]</t>
+          <t xml:space="preserve">GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
+          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8036,29 +8036,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[2]</t>
+          <t xml:space="preserve">GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
+          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[3]</t>
+          <t xml:space="preserve">GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
+          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8100,29 +8100,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[1]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[2]</t>
+          <t xml:space="preserve">preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
+          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[3]</t>
+          <t xml:space="preserve">preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8179,14 +8179,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
+          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[1]</t>
+          <t xml:space="preserve">preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
+          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[2]</t>
+          <t xml:space="preserve">preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8243,14 +8243,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
+          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.normal[1]</t>
+          <t xml:space="preserve">preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8275,14 +8275,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
+          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.normal[2]</t>
+          <t xml:space="preserve">preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8307,14 +8307,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
+          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.normal[1]</t>
+          <t xml:space="preserve">survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8339,14 +8339,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
+          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.normal[2]</t>
+          <t xml:space="preserve">survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8371,14 +8371,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8403,14 +8403,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8435,14 +8435,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
+          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8467,14 +8467,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
+          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8484,29 +8484,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.normal[1]</t>
+          <t xml:space="preserve">defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで走り切れました。…ありがとうございました</t>
+          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8516,59 +8516,283 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
+          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[2]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.normal[2]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで走り切れました。…ありがとうございました</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr" s="2">
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr" s="12">
+      <c r="D261" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr" s="2">
+      <c r="E261" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr" s="3">
+      <c r="F261" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H254"/>
+  <autoFilter ref="A1:H261"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7418,7 +7418,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7443,14 +7443,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
+          <t xml:space="preserve">……負けましたが、後悔はないです</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7475,14 +7475,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
+          <t xml:space="preserve">最高の試合で勝利できました。感無量です</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.normal[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7507,14 +7507,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。応援のおかげです</t>
+          <t xml:space="preserve">……勝てた。信じられません</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
+          <t xml:space="preserve">負けてしまいました…申し訳ないです</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.normal[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.normal[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7571,14 +7571,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し寂しいというか…不安が…</t>
+          <t xml:space="preserve">……すみません。次は、必ず</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7603,14 +7603,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
+          <t xml:space="preserve">勝てました。応援のおかげです</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.normal[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.normal[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7635,14 +7635,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると安心します</t>
+          <t xml:space="preserve">勝てました……応援、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.polite.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.polite.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7667,14 +7667,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">活躍が気になってしまいます</t>
+          <t xml:space="preserve">私情を持ち込むな、と自分に言い聞かせているが…難しい</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.normal[1]</t>
+          <t xml:space="preserve">GL-02.polite.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7699,14 +7699,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
+          <t xml:space="preserve">今日も精一杯練習させていただきます</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.polite.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7731,14 +7731,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
+          <t xml:space="preserve">少し寂しいというか…不安が…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.polite.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7763,14 +7763,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
+          <t xml:space="preserve">最近、居心地がとても良くなりました</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.normal[1]</t>
+          <t xml:space="preserve">GL-04.polite.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7795,14 +7795,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
+          <t xml:space="preserve">一緒にいると安心します</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.normal[1]</t>
+          <t xml:space="preserve">GL-05.polite.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7827,14 +7827,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
+          <t xml:space="preserve">活躍が気になってしまいます</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.polite.normal[1]</t>
+          <t xml:space="preserve">GL-06.polite.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
+          <t xml:space="preserve">出場できなかったのは残念ですが…次の機会を待ちます</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">GL-07.polite.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7891,14 +7891,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
+          <t xml:space="preserve">申し訳ありません…少し体調が…</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7908,29 +7908,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[1]</t>
+          <t xml:space="preserve">GL-08.polite.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
+          <t xml:space="preserve">連敗してしまって…皆さんに申し訳なくて…</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7940,29 +7940,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[2]</t>
+          <t xml:space="preserve">GL-09.polite.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">連勝させていただいています。ありがたいことです</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7972,29 +7972,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.normal[3]</t>
+          <t xml:space="preserve">GL-10.polite.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
+          <t xml:space="preserve">早く復帰して、皆さんのお役に立ちたいです</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8004,29 +8004,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[1]</t>
+          <t xml:space="preserve">GL-11.polite.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
+          <t xml:space="preserve">お見かけはしますが……特にお話することは</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8036,29 +8036,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[2]</t>
+          <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
+          <t xml:space="preserve">好調の波は去りましたが、得たものは大きかったです</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.normal[3]</t>
+          <t xml:space="preserve">preFinal.polite.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8083,14 +8083,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
+          <t xml:space="preserve">正直、身体はぼろぼろです。でも…最後まで立たせてください</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[1]</t>
+          <t xml:space="preserve">preFinal.polite.normal[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8115,14 +8115,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">ここまで繋いでもらった分、私が締めます。どんなに痛くても</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[2]</t>
+          <t xml:space="preserve">preFinal.polite.normal[3]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
+          <t xml:space="preserve">足が言うことを聞きません。…でも、この一戦だけは、退けないんです</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.normal[3]</t>
+          <t xml:space="preserve">preMatch.polite.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8179,14 +8179,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
+          <t xml:space="preserve">相手がどなたでも、全力でお相手します。ここで足を止めるわけにはいきませんから</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[1]</t>
+          <t xml:space="preserve">preMatch.polite.normal[2]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
+          <t xml:space="preserve">一戦一戦、丁寧に。仲間に繋ぐまで、退けません</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.normal[2]</t>
+          <t xml:space="preserve">preMatch.polite.normal[3]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8243,14 +8243,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
+          <t xml:space="preserve">まずは目の前の一人に集中します。それが、繋ぐってことですから</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.normal[1]</t>
+          <t xml:space="preserve">survivor.polite.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8275,14 +8275,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
+          <t xml:space="preserve">一人、倒しました。…息が上がってますけど、まだ退けません。次の方、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.normal[2]</t>
+          <t xml:space="preserve">survivor.polite.normal[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8307,14 +8307,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、来てください</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.normal[1]</t>
+          <t xml:space="preserve">survivor.polite.normal[3]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8339,14 +8339,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ大丈夫です。次の方、遠慮なく来てください</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.normal[2]</t>
+          <t xml:space="preserve">champion.polite.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8371,14 +8371,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
+          <t xml:space="preserve">三人でつないだ勝利です。私一人の力では、ここには立てませんでした</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">champion.polite.normal[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8403,14 +8403,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
+          <t xml:space="preserve">仲間が道を作ってくれました。その道を、最後まで歩けてよかったです</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">defiant.polite.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8435,14 +8435,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
+          <t xml:space="preserve">MVPをいただけたのはありがたいです。でも……団体が負けた悔しさの方が大きいです</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">defiant.polite.normal[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8467,14 +8467,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
+          <t xml:space="preserve">次こそは、仲間と一緒に勝ちたいです。この悔しさを忘れません</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8484,29 +8484,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.normal[1]</t>
+          <t xml:space="preserve">gauntlet.polite.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで走り切れました。…ありがとうございました</t>
+          <t xml:space="preserve">身体のあちこちが痛みます。でも、最後まで立ち続けられて……よかったです</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.normal[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8516,59 +8516,219 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.normal[1]</t>
+          <t xml:space="preserve">gauntlet.polite.normal[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
+          <t xml:space="preserve">何度も限界を感じました。それでも足が止まらなかったのは、きっと意地ですね</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力でお相手させていただきます。よろしくお願いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝ちました。この大舞台で、本当に……ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">対抗戦、勝たせていただきました。団体のために戦えて光栄です</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで走り切れました。…ありがとうございました</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.normal[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてもらえて嬉しいな。…そのぶんは試合で返すね</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.normal[1]</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr" s="2">
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr" s="12">
+      <c r="D259" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.normal[1]</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr" s="2">
+      <c r="E259" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr" s="3">
+      <c r="F259" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お声がけありがとうございます。精一杯やります</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H254"/>
+  <autoFilter ref="A1:H259"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願いがあります。あの方と、やらせていただけませんか。</t>
+          <t xml:space="preserve">社長、お願いがあります。三人で、挑ませていただけませんか。</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても、あの方とやってみたいんです。……お願いします。</t>
+          <t xml:space="preserve">どうしても、向こうへ三人で行きたいんです。……お願いします。</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">叶うなら、あの方と。……我慢できなくて、言いに来ました。</t>
+          <t xml:space="preserve">叶うなら、三人であちらへ。……我慢できなくて、言いに来ました。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×ノーマル.xlsx
@@ -7891,7 +7891,7 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私情を持ち込むな、と自分に言い聞かせているが…難しい</t>
+          <t xml:space="preserve">私情は持ち込まないと、決めているんです。……難しいですね</t>
         </is>
       </c>
     </row>
